--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run6/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run6/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
   <si>
     <t>Filename</t>
   </si>
@@ -808,757 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9280,0.0037,0.0344,0.0182</t>
-  </si>
-  <si>
-    <t>0.0117,0.0003,0.0014,0.9957</t>
-  </si>
-  <si>
-    <t>0.9942,0.0008,0.0000,0.0030</t>
-  </si>
-  <si>
-    <t>0.3421,0.0004,0.0003,0.9151</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0001</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9645,0.0037,0.0220,0.0039</t>
+  </si>
+  <si>
+    <t>0.0111,0.0006,0.0022,0.9940</t>
+  </si>
+  <si>
+    <t>0.8277,0.0054,0.0006,0.1774</t>
+  </si>
+  <si>
+    <t>0.0725,0.0003,0.0004,0.9852</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9961,0.0027,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9768,0.0024,0.0202,0.0004</t>
+  </si>
+  <si>
+    <t>0.2343,0.0210,0.8378,0.0048</t>
+  </si>
+  <si>
+    <t>0.0327,0.0045,0.9783,0.0004</t>
+  </si>
+  <si>
+    <t>0.3337,0.0073,0.7453,0.0175</t>
+  </si>
+  <si>
+    <t>0.9756,0.0062,0.0126,0.0009</t>
+  </si>
+  <si>
+    <t>0.0024,0.9948,0.0129,0.0003</t>
+  </si>
+  <si>
+    <t>0.0021,0.9946,0.0085,0.0018</t>
+  </si>
+  <si>
+    <t>0.0086,0.9849,0.0013,0.0033</t>
+  </si>
+  <si>
+    <t>0.0013,0.9969,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.9974,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.8740,0.0069,0.0662,0.0356</t>
+  </si>
+  <si>
+    <t>0.3673,0.0016,0.7354,0.0036</t>
+  </si>
+  <si>
+    <t>0.0134,0.0015,0.9816,0.0019</t>
+  </si>
+  <si>
+    <t>0.0224,0.0029,0.9783,0.0014</t>
+  </si>
+  <si>
+    <t>0.0059,0.0025,0.9916,0.0015</t>
+  </si>
+  <si>
+    <t>0.0434,0.0007,0.9718,0.0008</t>
+  </si>
+  <si>
+    <t>0.0092,0.0012,0.9927,0.0010</t>
+  </si>
+  <si>
+    <t>0.2868,0.7901,0.0198,0.0021</t>
+  </si>
+  <si>
+    <t>0.3074,0.5509,0.2400,0.0055</t>
+  </si>
+  <si>
+    <t>0.0019,0.0120,0.9936,0.0096</t>
+  </si>
+  <si>
+    <t>0.0265,0.9495,0.0153,0.0006</t>
+  </si>
+  <si>
+    <t>0.9069,0.0745,0.0025,0.0125</t>
+  </si>
+  <si>
+    <t>0.3392,0.0313,0.7038,0.0097</t>
+  </si>
+  <si>
+    <t>0.9237,0.1046,0.0043,0.0013</t>
+  </si>
+  <si>
+    <t>0.0129,0.9685,0.1650,0.0069</t>
+  </si>
+  <si>
+    <t>0.2071,0.0845,0.4999,0.0487</t>
+  </si>
+  <si>
+    <t>0.1321,0.0025,0.4207,0.1927</t>
+  </si>
+  <si>
+    <t>0.0730,0.0067,0.9150,0.0074</t>
+  </si>
+  <si>
+    <t>0.1166,0.0018,0.9144,0.0031</t>
+  </si>
+  <si>
+    <t>0.0233,0.0389,0.9765,0.0049</t>
+  </si>
+  <si>
+    <t>0.0070,0.9737,0.0098,0.0044</t>
+  </si>
+  <si>
+    <t>0.0071,0.0042,0.9886,0.0033</t>
+  </si>
+  <si>
+    <t>0.2855,0.3322,0.0378,0.2684</t>
+  </si>
+  <si>
+    <t>0.0082,0.9728,0.0105,0.0407</t>
+  </si>
+  <si>
+    <t>0.0029,0.9891,0.0077,0.0005</t>
+  </si>
+  <si>
+    <t>0.0008,0.9960,0.0062,0.0011</t>
+  </si>
+  <si>
+    <t>0.0057,0.0298,0.9802,0.0152</t>
+  </si>
+  <si>
+    <t>0.0032,0.1422,0.9956,0.0005</t>
+  </si>
+  <si>
+    <t>0.0231,0.0072,0.9692,0.0036</t>
+  </si>
+  <si>
+    <t>0.0065,0.0009,0.9863,0.0130</t>
+  </si>
+  <si>
+    <t>0.0026,0.0038,0.9955,0.0007</t>
+  </si>
+  <si>
+    <t>0.0275,0.0458,0.9347,0.0345</t>
+  </si>
+  <si>
+    <t>0.9954,0.0038,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9954,0.0017,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9944,0.0021,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.0080,0.0131,0.9921,0.0078</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9856,0.0134,0.0021,0.0016</t>
+  </si>
+  <si>
+    <t>0.0152,0.6367,0.9516,0.0030</t>
+  </si>
+  <si>
+    <t>0.0040,0.0127,0.9878,0.0090</t>
+  </si>
+  <si>
+    <t>0.0013,0.0041,0.9888,0.0108</t>
+  </si>
+  <si>
+    <t>0.0030,0.8011,0.9853,0.0020</t>
+  </si>
+  <si>
+    <t>0.0039,0.0018,0.9961,0.0004</t>
+  </si>
+  <si>
+    <t>0.0150,0.9783,0.0061,0.0023</t>
+  </si>
+  <si>
+    <t>0.0068,0.9885,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.9719,0.0037,0.0304,0.0012</t>
+  </si>
+  <si>
+    <t>0.9534,0.0173,0.0154,0.0125</t>
+  </si>
+  <si>
+    <t>0.0072,0.0040,0.9921,0.0024</t>
+  </si>
+  <si>
+    <t>0.0060,0.9340,0.4750,0.0004</t>
+  </si>
+  <si>
+    <t>0.0044,0.9039,0.7993,0.0009</t>
+  </si>
+  <si>
+    <t>0.0013,0.9909,0.4208,0.0009</t>
+  </si>
+  <si>
+    <t>0.0111,0.9167,0.9032,0.0031</t>
+  </si>
+  <si>
+    <t>0.0093,0.0001,0.0008,0.9965</t>
+  </si>
+  <si>
+    <t>0.0025,0.0007,0.0005,0.9986</t>
+  </si>
+  <si>
+    <t>0.0259,0.0004,0.0000,0.9942</t>
+  </si>
+  <si>
+    <t>0.0106,0.0020,0.0065,0.9908</t>
+  </si>
+  <si>
+    <t>0.0216,0.0014,0.0036,0.9897</t>
+  </si>
+  <si>
+    <t>0.0042,0.0016,0.0093,0.9938</t>
+  </si>
+  <si>
+    <t>0.0013,0.8200,0.9861,0.0008</t>
+  </si>
+  <si>
+    <t>0.0046,0.7685,0.9814,0.0012</t>
+  </si>
+  <si>
+    <t>0.0022,0.9643,0.7927,0.0011</t>
+  </si>
+  <si>
+    <t>0.0047,0.8761,0.8718,0.0011</t>
+  </si>
+  <si>
+    <t>0.0008,0.9865,0.8562,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.3723,0.9725,0.0020</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0016,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9917,0.0074,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9983,0.0011,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0005,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9964,0.0027,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9997,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9962,0.0022,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9982,0.0013,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9457,0.0142,0.0183,0.0048</t>
-  </si>
-  <si>
-    <t>0.0364,0.0150,0.9654,0.0018</t>
-  </si>
-  <si>
-    <t>0.8591,0.0062,0.1908,0.0005</t>
-  </si>
-  <si>
-    <t>0.0204,0.0026,0.9805,0.0010</t>
-  </si>
-  <si>
-    <t>0.7872,0.0044,0.2944,0.0017</t>
-  </si>
-  <si>
-    <t>0.0081,0.9895,0.0033,0.0008</t>
-  </si>
-  <si>
-    <t>0.0018,0.9953,0.0044,0.0010</t>
-  </si>
-  <si>
-    <t>0.0209,0.9763,0.0006,0.0034</t>
-  </si>
-  <si>
-    <t>0.0031,0.9925,0.0077,0.0005</t>
-  </si>
-  <si>
-    <t>0.0031,0.9943,0.0054,0.0002</t>
-  </si>
-  <si>
-    <t>0.5681,0.0069,0.5231,0.0102</t>
-  </si>
-  <si>
-    <t>0.3685,0.0017,0.7484,0.0036</t>
-  </si>
-  <si>
-    <t>0.0051,0.0013,0.9921,0.0016</t>
-  </si>
-  <si>
-    <t>0.1353,0.0066,0.9065,0.0022</t>
-  </si>
-  <si>
-    <t>0.3629,0.0210,0.7255,0.0027</t>
-  </si>
-  <si>
-    <t>0.0052,0.0008,0.9853,0.0124</t>
-  </si>
-  <si>
-    <t>0.0065,0.0097,0.9871,0.0088</t>
-  </si>
-  <si>
-    <t>0.6455,0.5421,0.0018,0.0032</t>
-  </si>
-  <si>
-    <t>0.5286,0.4638,0.0255,0.0208</t>
-  </si>
-  <si>
-    <t>0.0168,0.0061,0.9805,0.0073</t>
-  </si>
-  <si>
-    <t>0.0024,0.9933,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.8912,0.1458,0.0038,0.0032</t>
-  </si>
-  <si>
-    <t>0.9260,0.0084,0.0584,0.0003</t>
-  </si>
-  <si>
-    <t>0.8818,0.2364,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.0030,0.9920,0.0452,0.0023</t>
-  </si>
-  <si>
-    <t>0.0509,0.0903,0.7533,0.0198</t>
-  </si>
-  <si>
-    <t>0.3720,0.0376,0.3709,0.0781</t>
-  </si>
-  <si>
-    <t>0.0150,0.0125,0.9607,0.0206</t>
-  </si>
-  <si>
-    <t>0.1943,0.0020,0.8076,0.0110</t>
-  </si>
-  <si>
-    <t>0.0172,0.4145,0.9569,0.0258</t>
-  </si>
-  <si>
-    <t>0.0345,0.8614,0.1028,0.0154</t>
-  </si>
-  <si>
-    <t>0.0029,0.0044,0.9913,0.0094</t>
-  </si>
-  <si>
-    <t>0.1491,0.0940,0.0098,0.8632</t>
-  </si>
-  <si>
-    <t>0.0211,0.9198,0.0292,0.1836</t>
-  </si>
-  <si>
-    <t>0.0049,0.9766,0.0199,0.0034</t>
-  </si>
-  <si>
-    <t>0.0022,0.9902,0.0046,0.0060</t>
-  </si>
-  <si>
-    <t>0.0020,0.0181,0.9924,0.0050</t>
-  </si>
-  <si>
-    <t>0.0070,0.1178,0.9913,0.0023</t>
-  </si>
-  <si>
-    <t>0.0099,0.0168,0.9758,0.0072</t>
-  </si>
-  <si>
-    <t>0.0426,0.0009,0.9696,0.0048</t>
-  </si>
-  <si>
-    <t>0.0005,0.0049,0.9973,0.0018</t>
-  </si>
-  <si>
-    <t>0.0385,0.0056,0.9721,0.0025</t>
-  </si>
-  <si>
-    <t>0.9944,0.0058,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9958,0.0037,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9978,0.0006,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.0024,0.0288,0.9959,0.0061</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.0006,0.9612,0.9921,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.0172,0.9930,0.0109</t>
-  </si>
-  <si>
-    <t>0.0051,0.0082,0.9768,0.0102</t>
-  </si>
-  <si>
-    <t>0.0002,0.9688,0.9961,0.0002</t>
-  </si>
-  <si>
-    <t>0.0013,0.0006,0.9969,0.0033</t>
-  </si>
-  <si>
-    <t>0.2006,0.8414,0.0048,0.0009</t>
-  </si>
-  <si>
-    <t>0.0027,0.9925,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.9911,0.0012,0.0079,0.0005</t>
-  </si>
-  <si>
-    <t>0.8595,0.0459,0.1357,0.0119</t>
-  </si>
-  <si>
-    <t>0.0242,0.0034,0.9856,0.0007</t>
-  </si>
-  <si>
-    <t>0.0045,0.8972,0.9254,0.0005</t>
-  </si>
-  <si>
-    <t>0.0018,0.9521,0.6933,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.9929,0.7908,0.0005</t>
-  </si>
-  <si>
-    <t>0.0083,0.9521,0.8303,0.0034</t>
-  </si>
-  <si>
-    <t>0.0041,0.0004,0.0092,0.9962</t>
-  </si>
-  <si>
-    <t>0.0047,0.0011,0.0015,0.9970</t>
-  </si>
-  <si>
-    <t>0.0063,0.0014,0.0014,0.9963</t>
-  </si>
-  <si>
-    <t>0.0216,0.0042,0.0060,0.9842</t>
-  </si>
-  <si>
-    <t>0.0275,0.0003,0.0007,0.9923</t>
-  </si>
-  <si>
-    <t>0.0057,0.0005,0.0022,0.9959</t>
-  </si>
-  <si>
-    <t>0.0014,0.9414,0.9814,0.0006</t>
-  </si>
-  <si>
-    <t>0.0068,0.7269,0.9516,0.0005</t>
-  </si>
-  <si>
-    <t>0.0023,0.9867,0.4512,0.0008</t>
-  </si>
-  <si>
-    <t>0.0018,0.7468,0.9843,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.9908,0.9059,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.7548,0.9233,0.0010</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0013,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9942,0.0059,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9965,0.0031,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0008,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9983,0.0007,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0005,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9965,0.0034,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.0030,0.0014,0.9909,0.0073</t>
-  </si>
-  <si>
-    <t>0.0185,0.0123,0.9745,0.0036</t>
-  </si>
-  <si>
-    <t>0.9742,0.0054,0.0061,0.0044</t>
-  </si>
-  <si>
-    <t>0.0142,0.0055,0.9636,0.0163</t>
-  </si>
-  <si>
-    <t>0.0032,0.9942,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.0030,0.9945,0.0004,0.0026</t>
-  </si>
-  <si>
-    <t>0.0276,0.9641,0.0039,0.0048</t>
-  </si>
-  <si>
-    <t>0.0270,0.9684,0.0054,0.0030</t>
-  </si>
-  <si>
-    <t>0.0164,0.9839,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.0024,0.9944,0.0019,0.0016</t>
-  </si>
-  <si>
-    <t>0.8993,0.1866,0.0019,0.0018</t>
-  </si>
-  <si>
-    <t>0.5579,0.1173,0.2813,0.1511</t>
-  </si>
-  <si>
-    <t>0.9043,0.0030,0.1199,0.0035</t>
-  </si>
-  <si>
-    <t>0.5612,0.0723,0.3734,0.0190</t>
-  </si>
-  <si>
-    <t>0.3311,0.0251,0.6517,0.0111</t>
-  </si>
-  <si>
-    <t>0.0081,0.4753,0.0048,0.7770</t>
-  </si>
-  <si>
-    <t>0.0039,0.9926,0.0048,0.0015</t>
-  </si>
-  <si>
-    <t>0.0016,0.9911,0.0052,0.0046</t>
-  </si>
-  <si>
-    <t>0.0018,0.9890,0.0032,0.0180</t>
-  </si>
-  <si>
-    <t>0.0136,0.8763,0.8178,0.0019</t>
-  </si>
-  <si>
-    <t>0.0017,0.9966,0.0048,0.0003</t>
-  </si>
-  <si>
-    <t>0.8657,0.1830,0.0156,0.0014</t>
-  </si>
-  <si>
-    <t>0.7378,0.3294,0.0103,0.0014</t>
-  </si>
-  <si>
-    <t>0.9944,0.0048,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9922,0.0031,0.0008,0.0021</t>
-  </si>
-  <si>
-    <t>0.9981,0.0006,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9980,0.0005,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9939,0.0015,0.0002,0.0027</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9940,0.0031,0.0004,0.0012</t>
-  </si>
-  <si>
-    <t>0.9953,0.0017,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.0014,0.5870,0.9906,0.0003</t>
-  </si>
-  <si>
-    <t>0.0058,0.8927,0.8975,0.0008</t>
-  </si>
-  <si>
-    <t>0.0023,0.0149,0.9916,0.0005</t>
-  </si>
-  <si>
-    <t>0.0067,0.0046,0.9914,0.0017</t>
-  </si>
-  <si>
-    <t>0.9885,0.0011,0.0037,0.0009</t>
-  </si>
-  <si>
-    <t>0.9516,0.0098,0.0263,0.0044</t>
-  </si>
-  <si>
-    <t>0.2909,0.0004,0.8305,0.0021</t>
-  </si>
-  <si>
-    <t>0.8663,0.0157,0.0869,0.0317</t>
-  </si>
-  <si>
-    <t>0.0350,0.0002,0.0013,0.9867</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.0034,0.9995</t>
-  </si>
-  <si>
-    <t>0.0041,0.0027,0.0069,0.9939</t>
-  </si>
-  <si>
-    <t>0.0017,0.0004,0.0036,0.9982</t>
-  </si>
-  <si>
-    <t>0.0043,0.9365,0.3456,0.0018</t>
-  </si>
-  <si>
-    <t>0.9900,0.0100,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.1670,0.8179,0.0161,0.0331</t>
-  </si>
-  <si>
-    <t>0.9973,0.0006,0.0000,0.0013</t>
-  </si>
-  <si>
-    <t>0.4487,0.6632,0.0006,0.0024</t>
-  </si>
-  <si>
-    <t>0.9947,0.0009,0.0006,0.0014</t>
-  </si>
-  <si>
-    <t>0.7141,0.0096,0.0024,0.5026</t>
-  </si>
-  <si>
-    <t>0.9934,0.0010,0.0013,0.0018</t>
-  </si>
-  <si>
-    <t>0.0211,0.1573,0.9709,0.0255</t>
-  </si>
-  <si>
-    <t>0.3864,0.0002,0.0013,0.8808</t>
-  </si>
-  <si>
-    <t>0.9926,0.0004,0.0009,0.0057</t>
-  </si>
-  <si>
-    <t>0.5595,0.4770,0.0129,0.0152</t>
-  </si>
-  <si>
-    <t>0.9726,0.0127,0.0051,0.0031</t>
-  </si>
-  <si>
-    <t>0.9876,0.0073,0.0008,0.0017</t>
-  </si>
-  <si>
-    <t>0.5901,0.2510,0.0511,0.0263</t>
-  </si>
-  <si>
-    <t>0.9356,0.0261,0.0313,0.0028</t>
-  </si>
-  <si>
-    <t>0.9923,0.0041,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9948,0.0034,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9968,0.0012,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9980,0.0005,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9980,0.0001,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.9977,0.0004,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9926,0.0064,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9974,0.0005,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9985,0.0007,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9850,0.0117,0.0014,0.0012</t>
-  </si>
-  <si>
-    <t>0.5021,0.6281,0.0138,0.0017</t>
-  </si>
-  <si>
-    <t>0.3706,0.7469,0.0025,0.0024</t>
-  </si>
-  <si>
-    <t>0.4362,0.3205,0.4287,0.0052</t>
-  </si>
-  <si>
-    <t>0.9676,0.0379,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9862,0.0094,0.0009,0.0021</t>
-  </si>
-  <si>
-    <t>0.9957,0.0027,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9894,0.0116,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.0013,0.0048,0.9978,0.0066</t>
-  </si>
-  <si>
-    <t>0.9579,0.0226,0.0108,0.0065</t>
-  </si>
-  <si>
-    <t>0.0015,0.0019,0.9969,0.0005</t>
-  </si>
-  <si>
-    <t>0.0235,0.0470,0.9785,0.0024</t>
-  </si>
-  <si>
-    <t>0.0186,0.0044,0.9908,0.0005</t>
-  </si>
-  <si>
-    <t>0.0021,0.0149,0.9968,0.0002</t>
-  </si>
-  <si>
-    <t>0.0016,0.0024,0.9948,0.0047</t>
-  </si>
-  <si>
-    <t>0.0051,0.0010,0.9944,0.0003</t>
-  </si>
-  <si>
-    <t>0.0303,0.0035,0.9842,0.0008</t>
-  </si>
-  <si>
-    <t>0.0654,0.0354,0.8960,0.0087</t>
-  </si>
-  <si>
-    <t>0.0964,0.0189,0.9327,0.0054</t>
-  </si>
-  <si>
-    <t>0.1250,0.0143,0.8963,0.0021</t>
-  </si>
-  <si>
-    <t>0.2127,0.0322,0.7696,0.0042</t>
-  </si>
-  <si>
-    <t>0.0094,0.6783,0.4464,0.0004</t>
-  </si>
-  <si>
-    <t>0.7107,0.0163,0.2599,0.0009</t>
-  </si>
-  <si>
-    <t>0.6104,0.0739,0.2187,0.1727</t>
-  </si>
-  <si>
-    <t>0.2578,0.0176,0.7650,0.0027</t>
-  </si>
-  <si>
-    <t>0.3892,0.7639,0.0099,0.0007</t>
-  </si>
-  <si>
-    <t>0.0226,0.9765,0.0333,0.0010</t>
-  </si>
-  <si>
-    <t>0.9798,0.0214,0.0029,0.0020</t>
-  </si>
-  <si>
-    <t>0.9987,0.0014,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9301,0.1348,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.5039,0.5234,0.0189,0.0046</t>
-  </si>
-  <si>
-    <t>0.9920,0.0004,0.0044,0.0004</t>
-  </si>
-  <si>
-    <t>0.8484,0.0247,0.0327,0.0826</t>
-  </si>
-  <si>
-    <t>0.9166,0.0004,0.0833,0.0026</t>
-  </si>
-  <si>
-    <t>0.9208,0.0041,0.1207,0.0011</t>
-  </si>
-  <si>
-    <t>0.0042,0.0080,0.9904,0.0115</t>
-  </si>
-  <si>
-    <t>0.0608,0.0275,0.9286,0.0075</t>
-  </si>
-  <si>
-    <t>0.0755,0.0588,0.9275,0.0030</t>
-  </si>
-  <si>
-    <t>0.0555,0.2531,0.7873,0.0030</t>
-  </si>
-  <si>
-    <t>0.0032,0.0107,0.9918,0.0003</t>
-  </si>
-  <si>
-    <t>0.9982,0.0004,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.9977,0.0017,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0006,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9874,0.0174,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9950,0.0031,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9932,0.0036,0.0008,0.0011</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.9978,0.0004,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.1019,0.0614,0.8976,0.0381</t>
-  </si>
-  <si>
-    <t>0.0866,0.8439,0.0674,0.0034</t>
-  </si>
-  <si>
-    <t>0.8710,0.0068,0.1051,0.0155</t>
-  </si>
-  <si>
-    <t>0.0040,0.0019,0.9954,0.0009</t>
-  </si>
-  <si>
-    <t>0.0016,0.0023,0.9942,0.0042</t>
-  </si>
-  <si>
-    <t>0.0033,0.0405,0.9869,0.0116</t>
-  </si>
-  <si>
-    <t>0.0272,0.0008,0.9847,0.0005</t>
-  </si>
-  <si>
-    <t>0.0227,0.0060,0.9743,0.0065</t>
-  </si>
-  <si>
-    <t>0.0014,0.0012,0.9946,0.0047</t>
-  </si>
-  <si>
-    <t>0.0030,0.0069,0.9897,0.0030</t>
-  </si>
-  <si>
-    <t>0.0155,0.0064,0.9736,0.0043</t>
-  </si>
-  <si>
-    <t>0.8107,0.0011,0.0993,0.0346</t>
-  </si>
-  <si>
-    <t>0.3828,0.0053,0.6874,0.0123</t>
-  </si>
-  <si>
-    <t>0.9590,0.0025,0.0216,0.0073</t>
-  </si>
-  <si>
-    <t>0.9980,0.0009,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9988,0.0009,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0017,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0013,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.0120,0.0183,0.9707,0.0014</t>
-  </si>
-  <si>
-    <t>0.0006,0.0204,0.9965,0.0015</t>
-  </si>
-  <si>
-    <t>0.0230,0.0087,0.9682,0.0027</t>
-  </si>
-  <si>
-    <t>0.1124,0.1005,0.6514,0.0021</t>
-  </si>
-  <si>
-    <t>0.0441,0.0047,0.9691,0.0017</t>
-  </si>
-  <si>
-    <t>0.0359,0.0212,0.8647,0.1382</t>
-  </si>
-  <si>
-    <t>0.0970,0.0032,0.9353,0.0014</t>
-  </si>
-  <si>
-    <t>0.0053,0.0062,0.9859,0.0087</t>
-  </si>
-  <si>
-    <t>0.9847,0.0002,0.0002,0.0330</t>
-  </si>
-  <si>
-    <t>0.0158,0.0065,0.0014,0.9912</t>
-  </si>
-  <si>
-    <t>0.1227,0.0046,0.0003,0.9538</t>
-  </si>
-  <si>
-    <t>0.0438,0.0001,0.0001,0.9920</t>
-  </si>
-  <si>
-    <t>0.0030,0.0002,0.0000,0.9991</t>
-  </si>
-  <si>
-    <t>0.8059,0.0093,0.0004,0.2387</t>
+    <t>0.9982,0.0012,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.0064,0.0119,0.9916,0.0040</t>
+  </si>
+  <si>
+    <t>0.0478,0.0058,0.9724,0.0032</t>
+  </si>
+  <si>
+    <t>0.9817,0.0030,0.0017,0.0056</t>
+  </si>
+  <si>
+    <t>0.0032,0.0002,0.9953,0.0006</t>
+  </si>
+  <si>
+    <t>0.0053,0.9928,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.0017,0.9964,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.0546,0.9376,0.0094,0.0078</t>
+  </si>
+  <si>
+    <t>0.1730,0.8596,0.0025,0.0026</t>
+  </si>
+  <si>
+    <t>0.2590,0.8193,0.0006,0.0018</t>
+  </si>
+  <si>
+    <t>0.0117,0.9872,0.0025,0.0004</t>
+  </si>
+  <si>
+    <t>0.3724,0.6977,0.0015,0.0031</t>
+  </si>
+  <si>
+    <t>0.7817,0.0714,0.1457,0.0392</t>
+  </si>
+  <si>
+    <t>0.2936,0.0052,0.8105,0.0023</t>
+  </si>
+  <si>
+    <t>0.3461,0.2518,0.2015,0.1234</t>
+  </si>
+  <si>
+    <t>0.2798,0.0755,0.6963,0.0111</t>
+  </si>
+  <si>
+    <t>0.0043,0.0251,0.0060,0.9899</t>
+  </si>
+  <si>
+    <t>0.0117,0.9687,0.0262,0.0143</t>
+  </si>
+  <si>
+    <t>0.0002,0.9986,0.0005,0.0018</t>
+  </si>
+  <si>
+    <t>0.0049,0.9781,0.0030,0.0281</t>
+  </si>
+  <si>
+    <t>0.0060,0.9668,0.2651,0.0025</t>
+  </si>
+  <si>
+    <t>0.0197,0.9758,0.0767,0.0006</t>
+  </si>
+  <si>
+    <t>0.9323,0.1247,0.0025,0.0004</t>
+  </si>
+  <si>
+    <t>0.9490,0.0533,0.0075,0.0013</t>
+  </si>
+  <si>
+    <t>0.9980,0.0013,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9886,0.0023,0.0004,0.0076</t>
+  </si>
+  <si>
+    <t>0.9979,0.0011,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9959,0.0013,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9967,0.0010,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0017,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.7028,0.9841,0.0013</t>
+  </si>
+  <si>
+    <t>0.0241,0.2585,0.9094,0.0016</t>
+  </si>
+  <si>
+    <t>0.0046,0.0352,0.9871,0.0003</t>
+  </si>
+  <si>
+    <t>0.0280,0.0047,0.9858,0.0005</t>
+  </si>
+  <si>
+    <t>0.9749,0.0071,0.0103,0.0009</t>
+  </si>
+  <si>
+    <t>0.9716,0.0030,0.0176,0.0027</t>
+  </si>
+  <si>
+    <t>0.0191,0.0007,0.9888,0.0015</t>
+  </si>
+  <si>
+    <t>0.7713,0.1358,0.0755,0.0201</t>
+  </si>
+  <si>
+    <t>0.0580,0.0011,0.0024,0.9784</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0004,0.9996</t>
+  </si>
+  <si>
+    <t>0.0022,0.0152,0.0022,0.9961</t>
+  </si>
+  <si>
+    <t>0.0058,0.0001,0.0013,0.9973</t>
+  </si>
+  <si>
+    <t>0.0040,0.8981,0.7821,0.0025</t>
+  </si>
+  <si>
+    <t>0.9941,0.0035,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.0424,0.9480,0.0019,0.0158</t>
+  </si>
+  <si>
+    <t>0.9971,0.0007,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.1933,0.8606,0.0017,0.0028</t>
+  </si>
+  <si>
+    <t>0.9964,0.0008,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9205,0.0073,0.0117,0.1020</t>
+  </si>
+  <si>
+    <t>0.9939,0.0005,0.0007,0.0032</t>
+  </si>
+  <si>
+    <t>0.0058,0.0482,0.9834,0.0392</t>
+  </si>
+  <si>
+    <t>0.9111,0.0001,0.0024,0.1028</t>
+  </si>
+  <si>
+    <t>0.9259,0.0009,0.0130,0.0592</t>
+  </si>
+  <si>
+    <t>0.2490,0.7226,0.0402,0.0086</t>
+  </si>
+  <si>
+    <t>0.9674,0.0240,0.0019,0.0045</t>
+  </si>
+  <si>
+    <t>0.9340,0.0869,0.0027,0.0033</t>
+  </si>
+  <si>
+    <t>0.2904,0.5978,0.0031,0.0303</t>
+  </si>
+  <si>
+    <t>0.4137,0.0579,0.6445,0.0064</t>
+  </si>
+  <si>
+    <t>0.8155,0.1736,0.0298,0.0029</t>
+  </si>
+  <si>
+    <t>0.9966,0.0017,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9975,0.0010,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9972,0.0012,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9958,0.0009,0.0003,0.0020</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9871,0.0096,0.0026,0.0010</t>
+  </si>
+  <si>
+    <t>0.9958,0.0016,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9975,0.0010,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9485,0.0549,0.0022,0.0035</t>
+  </si>
+  <si>
+    <t>0.8449,0.2760,0.0012,0.0011</t>
+  </si>
+  <si>
+    <t>0.8683,0.2013,0.0005,0.0019</t>
+  </si>
+  <si>
+    <t>0.8555,0.1530,0.0314,0.0076</t>
+  </si>
+  <si>
+    <t>0.9950,0.0060,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.8178,0.1956,0.0022,0.0067</t>
+  </si>
+  <si>
+    <t>0.9951,0.0041,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.6340,0.4946,0.0004,0.0017</t>
+  </si>
+  <si>
+    <t>0.0023,0.0224,0.9981,0.0013</t>
+  </si>
+  <si>
+    <t>0.9612,0.0163,0.0233,0.0011</t>
+  </si>
+  <si>
+    <t>0.0012,0.0005,0.9970,0.0007</t>
+  </si>
+  <si>
+    <t>0.0738,0.0083,0.9500,0.0022</t>
+  </si>
+  <si>
+    <t>0.0959,0.0016,0.9503,0.0005</t>
+  </si>
+  <si>
+    <t>0.0124,0.0304,0.9849,0.0005</t>
+  </si>
+  <si>
+    <t>0.0355,0.0085,0.9741,0.0019</t>
+  </si>
+  <si>
+    <t>0.0121,0.0013,0.9930,0.0005</t>
+  </si>
+  <si>
+    <t>0.0019,0.0018,0.9974,0.0004</t>
+  </si>
+  <si>
+    <t>0.0780,0.0204,0.9171,0.0055</t>
+  </si>
+  <si>
+    <t>0.0541,0.0033,0.9688,0.0005</t>
+  </si>
+  <si>
+    <t>0.3838,0.0692,0.5348,0.1450</t>
+  </si>
+  <si>
+    <t>0.3538,0.1267,0.5112,0.0244</t>
+  </si>
+  <si>
+    <t>0.0450,0.0679,0.9125,0.0016</t>
+  </si>
+  <si>
+    <t>0.6141,0.0108,0.3807,0.0009</t>
+  </si>
+  <si>
+    <t>0.1055,0.0137,0.9224,0.0051</t>
+  </si>
+  <si>
+    <t>0.1068,0.0013,0.9495,0.0010</t>
+  </si>
+  <si>
+    <t>0.1442,0.9202,0.0047,0.0009</t>
+  </si>
+  <si>
+    <t>0.8068,0.3756,0.0030,0.0005</t>
+  </si>
+  <si>
+    <t>0.6481,0.5590,0.0048,0.0018</t>
+  </si>
+  <si>
+    <t>0.9536,0.1961,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9555,0.1692,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.8063,0.0787,0.1053,0.0081</t>
+  </si>
+  <si>
+    <t>0.9822,0.0004,0.0264,0.0003</t>
+  </si>
+  <si>
+    <t>0.9748,0.0033,0.0089,0.0044</t>
+  </si>
+  <si>
+    <t>0.0676,0.0047,0.9114,0.0308</t>
+  </si>
+  <si>
+    <t>0.9637,0.0072,0.0253,0.0011</t>
+  </si>
+  <si>
+    <t>0.0027,0.0023,0.9874,0.0458</t>
+  </si>
+  <si>
+    <t>0.0379,0.0221,0.9412,0.0043</t>
+  </si>
+  <si>
+    <t>0.0477,0.0051,0.9636,0.0013</t>
+  </si>
+  <si>
+    <t>0.0375,0.0036,0.9672,0.0026</t>
+  </si>
+  <si>
+    <t>0.0072,0.0107,0.9772,0.0014</t>
+  </si>
+  <si>
+    <t>0.9963,0.0007,0.0000,0.0016</t>
+  </si>
+  <si>
+    <t>0.9977,0.0009,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9983,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9938,0.0037,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9941,0.0027,0.0003,0.0017</t>
+  </si>
+  <si>
+    <t>0.9938,0.0013,0.0002,0.0031</t>
+  </si>
+  <si>
+    <t>0.9974,0.0008,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.0987,0.0064,0.9586,0.0035</t>
+  </si>
+  <si>
+    <t>0.0471,0.1725,0.8637,0.0037</t>
+  </si>
+  <si>
+    <t>0.9677,0.0036,0.0081,0.0191</t>
+  </si>
+  <si>
+    <t>0.0040,0.0022,0.9933,0.0015</t>
+  </si>
+  <si>
+    <t>0.0038,0.0138,0.9905,0.0018</t>
+  </si>
+  <si>
+    <t>0.0086,0.0235,0.9879,0.0005</t>
+  </si>
+  <si>
+    <t>0.0983,0.0032,0.9655,0.0004</t>
+  </si>
+  <si>
+    <t>0.0426,0.0232,0.9383,0.0171</t>
+  </si>
+  <si>
+    <t>0.0171,0.0014,0.9912,0.0004</t>
+  </si>
+  <si>
+    <t>0.0199,0.0044,0.9706,0.0050</t>
+  </si>
+  <si>
+    <t>0.0068,0.0061,0.9850,0.0025</t>
+  </si>
+  <si>
+    <t>0.9211,0.0031,0.1256,0.0011</t>
+  </si>
+  <si>
+    <t>0.7019,0.0038,0.4323,0.0053</t>
+  </si>
+  <si>
+    <t>0.8155,0.0008,0.1529,0.0105</t>
+  </si>
+  <si>
+    <t>0.9979,0.0009,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9955,0.0067,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0022,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9987,0.0006,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9957,0.0070,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0000,0.0009</t>
+  </si>
+  <si>
+    <t>0.0134,0.0071,0.9731,0.0026</t>
+  </si>
+  <si>
+    <t>0.0030,0.0126,0.9946,0.0005</t>
+  </si>
+  <si>
+    <t>0.0336,0.0115,0.9494,0.0132</t>
+  </si>
+  <si>
+    <t>0.0150,0.1502,0.8517,0.0025</t>
+  </si>
+  <si>
+    <t>0.0147,0.0012,0.9863,0.0027</t>
+  </si>
+  <si>
+    <t>0.5203,0.0040,0.2297,0.1163</t>
+  </si>
+  <si>
+    <t>0.1079,0.0046,0.9151,0.0075</t>
+  </si>
+  <si>
+    <t>0.0678,0.0066,0.9285,0.0088</t>
+  </si>
+  <si>
+    <t>0.9948,0.0001,0.0000,0.0152</t>
+  </si>
+  <si>
+    <t>0.0491,0.0015,0.0004,0.9847</t>
+  </si>
+  <si>
+    <t>0.2100,0.0013,0.0001,0.9412</t>
+  </si>
+  <si>
+    <t>0.0279,0.0005,0.0002,0.9916</t>
+  </si>
+  <si>
+    <t>0.0062,0.0002,0.0001,0.9983</t>
+  </si>
+  <si>
+    <t>0.8560,0.0073,0.0001,0.1142</t>
   </si>
 </sst>
 </file>
@@ -1944,7 +1956,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1958,7 +1970,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1972,7 +1984,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1986,7 +1998,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2000,7 +2012,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2014,7 +2026,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2028,7 +2040,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2042,7 +2054,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2056,7 +2068,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2070,7 +2082,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2084,7 +2096,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2098,7 +2110,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2112,7 +2124,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2126,7 +2138,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2137,10 +2149,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2154,7 +2166,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2168,7 +2180,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2182,7 +2194,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2196,7 +2208,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2210,7 +2222,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2224,7 +2236,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2238,7 +2250,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2249,10 +2261,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2266,7 +2278,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2280,7 +2292,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2294,7 +2306,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2308,7 +2320,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2322,7 +2334,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2336,7 +2348,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2350,7 +2362,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2361,10 +2373,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2378,7 +2390,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2392,7 +2404,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2406,7 +2418,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2417,10 +2429,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2434,7 +2446,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2448,7 +2460,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2459,10 +2471,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2473,10 +2485,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2490,7 +2502,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2504,7 +2516,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2518,7 +2530,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2532,7 +2544,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2546,7 +2558,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2557,10 +2569,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2574,7 +2586,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2588,7 +2600,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2602,7 +2614,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2616,7 +2628,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2630,7 +2642,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2644,7 +2656,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2658,7 +2670,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2672,7 +2684,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2686,7 +2698,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2700,7 +2712,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2714,7 +2726,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2728,7 +2740,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2742,7 +2754,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2756,7 +2768,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2770,7 +2782,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>270</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2784,7 +2796,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2798,7 +2810,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2812,7 +2824,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2826,7 +2838,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2840,7 +2852,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2854,7 +2866,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2868,7 +2880,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2882,7 +2894,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2896,7 +2908,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2910,7 +2922,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2924,7 +2936,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2935,10 +2947,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2952,7 +2964,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2963,10 +2975,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2980,7 +2992,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2994,7 +3006,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3008,7 +3020,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3022,7 +3034,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3036,7 +3048,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3050,7 +3062,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3064,7 +3076,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3078,7 +3090,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3092,7 +3104,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3103,10 +3115,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3120,7 +3132,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3134,7 +3146,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3145,10 +3157,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3162,7 +3174,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3176,7 +3188,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3190,7 +3202,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3204,7 +3216,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3218,7 +3230,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3232,7 +3244,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3246,7 +3258,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3260,7 +3272,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3274,7 +3286,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3288,7 +3300,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3302,7 +3314,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3316,7 +3328,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3330,7 +3342,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3344,7 +3356,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3358,7 +3370,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3372,7 +3384,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3386,7 +3398,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3400,7 +3412,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3414,7 +3426,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3428,7 +3440,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3442,7 +3454,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3456,7 +3468,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3470,7 +3482,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3484,7 +3496,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3498,7 +3510,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3512,7 +3524,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3523,10 +3535,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3540,7 +3552,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3551,10 +3563,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3565,10 +3577,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3582,7 +3594,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3596,7 +3608,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3610,7 +3622,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3624,7 +3636,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3638,7 +3650,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3649,10 +3661,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3666,7 +3678,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3680,7 +3692,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3694,7 +3706,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3708,7 +3720,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3722,7 +3734,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3736,7 +3748,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3750,7 +3762,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3764,7 +3776,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3778,7 +3790,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3792,7 +3804,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3806,7 +3818,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3820,7 +3832,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3831,10 +3843,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3848,7 +3860,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3862,7 +3874,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3876,7 +3888,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3890,7 +3902,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3904,7 +3916,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3918,7 +3930,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3932,7 +3944,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3946,7 +3958,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3960,7 +3972,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3974,7 +3986,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3985,10 +3997,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4002,7 +4014,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4016,7 +4028,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4030,7 +4042,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4044,7 +4056,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4058,7 +4070,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4069,10 +4081,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4086,7 +4098,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4100,7 +4112,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4111,10 +4123,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4128,7 +4140,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4139,10 +4151,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4156,7 +4168,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4170,7 +4182,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4181,10 +4193,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4195,10 +4207,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D163" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4212,7 +4224,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4226,7 +4238,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4240,7 +4252,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4254,7 +4266,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4268,7 +4280,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4282,7 +4294,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4296,7 +4308,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4310,7 +4322,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4324,7 +4336,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4338,7 +4350,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4349,10 +4361,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4363,10 +4375,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4380,7 +4392,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4394,7 +4406,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4408,7 +4420,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4422,7 +4434,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4436,7 +4448,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4450,7 +4462,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4464,7 +4476,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4478,7 +4490,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4492,7 +4504,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4506,7 +4518,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4520,7 +4532,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4534,7 +4546,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4548,7 +4560,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4562,7 +4574,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4576,7 +4588,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4590,7 +4602,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4604,7 +4616,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4618,7 +4630,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4629,10 +4641,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4646,7 +4658,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4657,10 +4669,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4674,7 +4686,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4688,7 +4700,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4699,10 +4711,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4713,10 +4725,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D200" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4730,7 +4742,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4744,7 +4756,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4755,10 +4767,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4772,7 +4784,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4786,7 +4798,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4797,10 +4809,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4814,7 +4826,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4828,7 +4840,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4842,7 +4854,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4856,7 +4868,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4870,7 +4882,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4884,7 +4896,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4898,7 +4910,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4912,7 +4924,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4926,7 +4938,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4940,7 +4952,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4954,7 +4966,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4968,7 +4980,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4982,7 +4994,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4996,7 +5008,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5010,7 +5022,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5021,10 +5033,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5038,7 +5050,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5052,7 +5064,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5066,7 +5078,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5080,7 +5092,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5094,7 +5106,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5108,7 +5120,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5122,7 +5134,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5136,7 +5148,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5150,7 +5162,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5164,7 +5176,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5175,10 +5187,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5192,7 +5204,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5206,7 +5218,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5220,7 +5232,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5234,7 +5246,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>355</v>
+        <v>499</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5248,7 +5260,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5262,7 +5274,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5276,7 +5288,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5290,7 +5302,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5304,7 +5316,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5318,7 +5330,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5332,7 +5344,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5346,7 +5358,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5360,7 +5372,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5374,7 +5386,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5385,10 +5397,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5402,7 +5414,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5416,7 +5428,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5430,7 +5442,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5444,7 +5456,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5458,7 +5470,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5472,7 +5484,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5486,7 +5498,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5500,7 +5512,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
